--- a/data/trans_dic/IP37-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han trabajado anteriormente</t>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,34; 65,45</t>
+          <t>44,7; 65,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,32; 77,64</t>
+          <t>58,96; 78,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,24; 85,08</t>
+          <t>64,24; 84,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,01; 83,34</t>
+          <t>50,08; 83,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,36; 78,57</t>
+          <t>57,04; 77,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,34; 74,4</t>
+          <t>54,69; 75,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,43; 77,57</t>
+          <t>54,47; 77,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,9; 83,59</t>
+          <t>59,42; 83,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,27; 68,53</t>
+          <t>53,49; 68,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,71; 73,54</t>
+          <t>60,02; 73,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63,44; 79,11</t>
+          <t>63,14; 78,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,38; 80,41</t>
+          <t>60,55; 81,6</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,41; 67,59</t>
+          <t>56,64; 68,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,49; 82,94</t>
+          <t>74,56; 83,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,18; 80,08</t>
+          <t>71,39; 79,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,86; 78,46</t>
+          <t>60,83; 79,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,88; 66,28</t>
+          <t>56,14; 66,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,39; 78,96</t>
+          <t>70,28; 78,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,04; 77,1</t>
+          <t>67,6; 77,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>61,24; 73,76</t>
+          <t>61,11; 74,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,6; 65,85</t>
+          <t>57,87; 65,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,45; 79,65</t>
+          <t>73,92; 79,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,9; 77,0</t>
+          <t>70,91; 76,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,62; 75,19</t>
+          <t>63,15; 74,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,71; 73,89</t>
+          <t>51,2; 73,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,07; 84,97</t>
+          <t>66,38; 84,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,07; 87,72</t>
+          <t>70,22; 87,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70,88; 96,59</t>
+          <t>72,81; 96,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,72; 78,39</t>
+          <t>56,85; 79,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,93; 83,21</t>
+          <t>64,77; 83,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,62; 89,06</t>
+          <t>71,32; 88,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,1; 93,15</t>
+          <t>63,01; 95,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,45; 72,79</t>
+          <t>57,52; 73,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,22; 81,93</t>
+          <t>69,38; 81,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,89; 86,35</t>
+          <t>73,85; 86,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,7; 93,37</t>
+          <t>73,47; 92,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,86; 66,29</t>
+          <t>56,54; 65,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,46; 80,34</t>
+          <t>73,19; 80,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,36; 79,79</t>
+          <t>72,55; 79,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,64; 79,49</t>
+          <t>63,07; 79,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,76; 67,42</t>
+          <t>59,07; 67,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,67; 76,99</t>
+          <t>69,64; 76,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,34; 76,82</t>
+          <t>69,66; 77,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,93; 75,68</t>
+          <t>63,54; 75,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,98; 65,36</t>
+          <t>59,08; 65,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,76; 77,81</t>
+          <t>72,47; 77,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,04; 77,25</t>
+          <t>72,01; 77,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,78; 75,57</t>
+          <t>65,86; 75,95</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32340</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45104</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35406</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23353</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35955</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41984</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33099</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>27664</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>68295</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>87087</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68505</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>51017</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>26252; 38508</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38744; 51286</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29921; 39372</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17262; 28874</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>30043; 40652</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>34983; 47981</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26772; 38227</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>22528; 31706</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>59589; 75965</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>77827; 95079</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>60444; 75249</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>43833; 59069</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>122387</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>206436</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>194765</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>137584</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>214194</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>187918</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>131625</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>259386</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>420629</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>382684</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>269208</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>110843; 133637</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>194467; 216740</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>183799; 204965</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122292; 160793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>125365; 148917</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>201630; 225450</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>175091; 199508</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>118311; 143694</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>242472; 273708</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>404876; 436359</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>366228; 397058</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>249198; 295127</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>29574</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48017</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46642</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19520</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28046</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47403</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47459</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20676</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>57620</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>95420</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94100</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>40196</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>24098; 34717</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41530; 53017</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40930; 51271</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16113; 21417</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23294; 32649</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>40929; 52785</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>41843; 51923</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>15699; 23813</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>50646; 64732</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>87239; 102720</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>86377; 100951</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>34566; 43619</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>184301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>299556</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>276814</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>180457</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>303581</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>179964</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>385300</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>603137</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>545289</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>360421</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>170456; 197088</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>284784; 312239</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>262856; 288726</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>162495; 204839</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>187220; 214065</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>288350; 318207</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>255559; 283291</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>162932; 192773</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>365387; 404206</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>582017; 621744</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>525049; 563719</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>338564; 390416</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP37-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,7; 65,57</t>
+          <t>44,98; 65,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,96; 78,05</t>
+          <t>58,54; 77,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,24; 84,54</t>
+          <t>65,06; 85,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,08; 83,76</t>
+          <t>50,68; 84,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,04; 77,18</t>
+          <t>56,67; 77,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,69; 75,01</t>
+          <t>55,66; 75,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,47; 77,77</t>
+          <t>55,05; 78,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,42; 83,62</t>
+          <t>58,42; 84,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,49; 68,19</t>
+          <t>53,99; 68,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,02; 73,32</t>
+          <t>60,13; 73,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63,14; 78,61</t>
+          <t>63,84; 79,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,55; 81,6</t>
+          <t>59,46; 80,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>56,64; 68,29</t>
+          <t>57,33; 67,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,56; 83,1</t>
+          <t>74,43; 83,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,39; 79,61</t>
+          <t>70,4; 79,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,83; 79,98</t>
+          <t>61,04; 81,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,14; 66,69</t>
+          <t>56,19; 66,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,28; 78,58</t>
+          <t>70,29; 78,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,6; 77,02</t>
+          <t>68,02; 76,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>61,11; 74,22</t>
+          <t>61,48; 73,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57,87; 65,33</t>
+          <t>58,13; 65,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,92; 79,67</t>
+          <t>73,88; 79,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,91; 76,88</t>
+          <t>70,72; 77,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,15; 74,78</t>
+          <t>63,13; 75,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,2; 73,76</t>
+          <t>50,47; 73,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,38; 84,74</t>
+          <t>66,6; 85,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,22; 87,97</t>
+          <t>69,82; 87,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,81; 96,78</t>
+          <t>73,04; 96,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,85; 79,68</t>
+          <t>55,57; 78,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,77; 83,54</t>
+          <t>65,73; 83,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,32; 88,5</t>
+          <t>70,49; 87,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,01; 95,57</t>
+          <t>64,81; 95,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,52; 73,52</t>
+          <t>57,09; 73,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,38; 81,69</t>
+          <t>68,67; 81,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,85; 86,32</t>
+          <t>74,01; 86,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,47; 92,72</t>
+          <t>72,91; 93,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,54; 65,37</t>
+          <t>56,86; 65,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,19; 80,25</t>
+          <t>73,15; 80,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,55; 79,69</t>
+          <t>72,64; 79,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,07; 79,5</t>
+          <t>63,53; 79,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,07; 67,54</t>
+          <t>59,33; 68,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,64; 76,85</t>
+          <t>69,29; 76,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,66; 77,22</t>
+          <t>69,4; 77,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,54; 75,18</t>
+          <t>64,27; 75,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,08; 65,36</t>
+          <t>59,25; 65,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,47; 77,41</t>
+          <t>72,43; 77,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,31</t>
+          <t>72,23; 77,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,86; 75,95</t>
+          <t>65,95; 75,52</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26252; 38508</t>
+          <t>26415; 38728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38744; 51286</t>
+          <t>38469; 50710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29921; 39372</t>
+          <t>30302; 39842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17262; 28874</t>
+          <t>17471; 29220</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30043; 40652</t>
+          <t>29847; 40775</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34983; 47981</t>
+          <t>35605; 48183</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26772; 38227</t>
+          <t>27057; 38490</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22528; 31706</t>
+          <t>22151; 31967</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59589; 75965</t>
+          <t>60140; 76447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77827; 95079</t>
+          <t>77979; 95771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60444; 75249</t>
+          <t>61111; 75765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43833; 59069</t>
+          <t>43041; 58173</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>110843; 133637</t>
+          <t>112184; 132658</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194467; 216740</t>
+          <t>194146; 216588</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183799; 204965</t>
+          <t>181259; 204909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122292; 160793</t>
+          <t>122725; 163602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125365; 148917</t>
+          <t>125463; 148890</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>201630; 225450</t>
+          <t>201652; 225647</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>175091; 199508</t>
+          <t>176176; 199076</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>118311; 143694</t>
+          <t>119017; 142551</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>242472; 273708</t>
+          <t>243581; 274772</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>404876; 436359</t>
+          <t>404647; 436674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>366228; 397058</t>
+          <t>365283; 398616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>249198; 295127</t>
+          <t>249116; 297827</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24098; 34717</t>
+          <t>23754; 34595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41530; 53017</t>
+          <t>41665; 53214</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40930; 51271</t>
+          <t>40693; 50828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16113; 21417</t>
+          <t>16163; 21339</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23294; 32649</t>
+          <t>22771; 32181</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40929; 52785</t>
+          <t>41533; 52874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41843; 51923</t>
+          <t>41360; 51568</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15699; 23813</t>
+          <t>16147; 23867</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50646; 64732</t>
+          <t>50263; 64269</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87239; 102720</t>
+          <t>86349; 102936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86377; 100951</t>
+          <t>86558; 100792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34566; 43619</t>
+          <t>34300; 43814</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>170456; 197088</t>
+          <t>171440; 198509</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>284784; 312239</t>
+          <t>284619; 312540</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>262856; 288726</t>
+          <t>263178; 289108</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>162495; 204839</t>
+          <t>163670; 205255</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>187220; 214065</t>
+          <t>188033; 215929</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>288350; 318207</t>
+          <t>286906; 317355</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>255559; 283291</t>
+          <t>254604; 282717</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162932; 192773</t>
+          <t>164795; 193078</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>365387; 404206</t>
+          <t>366403; 403945</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>582017; 621744</t>
+          <t>581685; 622421</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>525049; 563719</t>
+          <t>526669; 564503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>338564; 390416</t>
+          <t>339051; 388210</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP37-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68,26%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65,64%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67,34%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72,78%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>55,07%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>68,64%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>76,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67,74%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,34%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,98; 65,95</t>
+          <t>57,36; 78,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,54; 77,17</t>
+          <t>54,34; 74,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,06; 85,55</t>
+          <t>54,43; 77,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,68; 84,77</t>
+          <t>57,08; 83,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,67; 77,42</t>
+          <t>44,34; 65,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,66; 75,33</t>
+          <t>58,32; 77,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,05; 78,31</t>
+          <t>62,24; 85,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,42; 84,31</t>
+          <t>39,93; 74,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,99; 68,63</t>
+          <t>54,27; 68,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,13; 73,86</t>
+          <t>59,71; 73,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63,84; 79,15</t>
+          <t>63,44; 79,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,46; 80,36</t>
+          <t>55,14; 76,15</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>62,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>79,15%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>75,65%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>68,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>74,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,55%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>64,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,33; 67,79</t>
+          <t>55,88; 66,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,43; 83,04</t>
+          <t>70,39; 78,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,4; 79,59</t>
+          <t>68,04; 77,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,04; 81,38</t>
+          <t>59,21; 72,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,19; 66,68</t>
+          <t>56,41; 67,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,29; 78,65</t>
+          <t>74,49; 82,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,02; 76,86</t>
+          <t>71,18; 80,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>61,48; 73,63</t>
+          <t>56,37; 68,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,13; 65,58</t>
+          <t>57,6; 65,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,88; 79,72</t>
+          <t>73,45; 79,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,72; 77,18</t>
+          <t>70,9; 77,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,13; 75,47</t>
+          <t>60,37; 69,17</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68,44%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80,89%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>62,84%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>76,75%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>80,02%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,44%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,89%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,47; 73,5</t>
+          <t>56,72; 78,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,6; 85,06</t>
+          <t>64,93; 83,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,82; 87,21</t>
+          <t>71,62; 89,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,04; 96,42</t>
+          <t>64,82; 95,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,57; 78,54</t>
+          <t>50,71; 73,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,73; 83,68</t>
+          <t>66,07; 84,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,49; 87,89</t>
+          <t>70,07; 87,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,81; 95,79</t>
+          <t>70,21; 96,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,09; 73,0</t>
+          <t>56,45; 72,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,67; 81,86</t>
+          <t>68,22; 81,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74,01; 86,18</t>
+          <t>73,89; 86,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72,91; 93,13</t>
+          <t>75,39; 93,86</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>73,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,86; 65,84</t>
+          <t>58,76; 67,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,15; 80,32</t>
+          <t>69,67; 76,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,64; 79,79</t>
+          <t>69,34; 76,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,53; 79,67</t>
+          <t>63,97; 74,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,33; 68,13</t>
+          <t>56,86; 66,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,29; 76,65</t>
+          <t>73,46; 80,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,07</t>
+          <t>72,36; 79,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,27; 75,3</t>
+          <t>58,93; 69,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,25; 65,32</t>
+          <t>58,98; 65,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 77,5</t>
+          <t>72,76; 77,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,23; 77,42</t>
+          <t>72,04; 77,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,95; 75,52</t>
+          <t>63,26; 71,21</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35955</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41984</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33099</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25813</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>32340</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>45104</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>35406</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23353</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35955</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41984</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33099</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>42287</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26415; 38728</t>
+          <t>30211; 41382</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38469; 50710</t>
+          <t>34761; 47590</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30302; 39842</t>
+          <t>26751; 38129</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17471; 29220</t>
+          <t>20245; 29751</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29847; 40775</t>
+          <t>26038; 38436</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35605; 48183</t>
+          <t>38323; 51019</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27057; 38490</t>
+          <t>28989; 39623</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22151; 31967</t>
+          <t>11200; 20878</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60140; 76447</t>
+          <t>60456; 76339</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77979; 95771</t>
+          <t>77434; 95366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61111; 75765</t>
+          <t>60727; 75724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43041; 58173</t>
+          <t>35021; 48367</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>298</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>162</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>214194</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>187918</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>117106</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>122387</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>206436</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>194765</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137584</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>136998</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>214194</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>187918</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>131625</t>
+          <t>108836</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>269208</t>
+          <t>225941</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112184; 132658</t>
+          <t>124784; 148001</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194146; 216588</t>
+          <t>201951; 226535</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181259; 204909</t>
+          <t>176245; 199717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122725; 163602</t>
+          <t>104592; 127349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125463; 148890</t>
+          <t>110397; 132271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>201652; 225647</t>
+          <t>194295; 216330</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>176176; 199076</t>
+          <t>183258; 206181</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>119017; 142551</t>
+          <t>97475; 118729</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>243581; 274772</t>
+          <t>241346; 275902</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>404647; 436674</t>
+          <t>402304; 436277</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>365283; 398616</t>
+          <t>366171; 397676</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>249116; 297827</t>
+          <t>211044; 241786</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28046</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47459</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19538</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>29574</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>48017</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>46642</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28046</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>47403</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47459</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40196</t>
+          <t>38915</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23754; 34595</t>
+          <t>23240; 32122</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41665; 53214</t>
+          <t>41030; 52579</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40693; 50828</t>
+          <t>42023; 52255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16163; 21339</t>
+          <t>14878; 21913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22771; 32181</t>
+          <t>23865; 34779</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41533; 52874</t>
+          <t>41336; 53158</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41360; 51568</t>
+          <t>40837; 51125</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16147; 23867</t>
+          <t>15540; 21345</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50263; 64269</t>
+          <t>49701; 64090</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86349; 102936</t>
+          <t>85788; 103030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86558; 100792</t>
+          <t>86416; 100996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34300; 43814</t>
+          <t>33990; 42315</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>214</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>303581</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>303581</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>171440; 198509</t>
+          <t>186230; 213697</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>284619; 312540</t>
+          <t>288453; 318785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>263178; 289108</t>
+          <t>254378; 281816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163670; 205255</t>
+          <t>150383; 175572</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>188033; 215929</t>
+          <t>171439; 199853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>286906; 317355</t>
+          <t>285815; 312603</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>254604; 282717</t>
+          <t>262174; 289089</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>164795; 193078</t>
+          <t>131478; 155723</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>366403; 403945</t>
+          <t>364768; 404199</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>581685; 622421</t>
+          <t>584383; 624947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>526669; 564503</t>
+          <t>525292; 563262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>339051; 388210</t>
+          <t>289848; 326240</t>
         </is>
       </c>
     </row>
